--- a/Web crawling/Review/reviews_by_store/S040.xlsx
+++ b/Web crawling/Review/reviews_by_store/S040.xlsx
@@ -46,8 +46,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K725"/>
+  <dimension ref="A1:K726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40219,6 +40222,63 @@
         </is>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" s="1" t="inlineStr">
+        <is>
+          <t>S040-0725</t>
+        </is>
+      </c>
+      <c r="B726" s="1" t="inlineStr">
+        <is>
+          <t>S040</t>
+        </is>
+      </c>
+      <c r="C726" s="1" t="inlineStr">
+        <is>
+          <t>메이드리밍 메이드카페</t>
+        </is>
+      </c>
+      <c r="D726" s="1" t="inlineStr">
+        <is>
+          <t>5dc556638f87a842bc9d6322</t>
+        </is>
+      </c>
+      <c r="E726" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F726" s="1" t="inlineStr">
+        <is>
+          <t>저녁</t>
+        </is>
+      </c>
+      <c r="G726" s="1" t="inlineStr">
+        <is>
+          <t>바로 입장</t>
+        </is>
+      </c>
+      <c r="H726" s="1" t="inlineStr">
+        <is>
+          <t>예약 없이 이용, 일상, 혼자</t>
+        </is>
+      </c>
+      <c r="I726" s="1" t="inlineStr">
+        <is>
+          <t>플러스오토코 라이브 너무 재밌었어요!
+파에님 최고ㅋㅋ
+라이브 넘 잘하세요</t>
+        </is>
+      </c>
+      <c r="J726" s="1" t="inlineStr">
+        <is>
+          <t>8.25.화</t>
+        </is>
+      </c>
+      <c r="K726" s="1" t="inlineStr">
+        <is>
+          <t>39번째 방문</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
